--- a/output/yearly_surface_area_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_3_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497625440984</v>
+        <v>10.84497635390578</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789071670799</v>
+        <v>37.78907201749033</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.432991795301848</v>
+        <v>5.737333583618359</v>
       </c>
       <c r="C2" t="n">
-        <v>10.07764018409351</v>
+        <v>8.948630324209677</v>
       </c>
       <c r="D2" t="n">
-        <v>18.76218037586079</v>
+        <v>32.71281525320797</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.74999849278233</v>
+        <v>16.29701189049705</v>
       </c>
       <c r="C3" t="n">
-        <v>33.63467634749573</v>
+        <v>17.82362957060084</v>
       </c>
       <c r="D3" t="n">
-        <v>60.56401587498573</v>
+        <v>91.22890541713485</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.35197406640165</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="C4" t="n">
-        <v>103.9268302238631</v>
+        <v>56.43674852633215</v>
       </c>
       <c r="D4" t="n">
-        <v>74.80230282967722</v>
+        <v>123.6835210241259</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.08738521234053</v>
+        <v>41.01251034491051</v>
       </c>
       <c r="C5" t="n">
-        <v>148.5875150377548</v>
+        <v>106.4705385255666</v>
       </c>
       <c r="D5" t="n">
-        <v>56.42594930158544</v>
+        <v>88.33274968960677</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.80638438474769</v>
+        <v>36.26674194258143</v>
       </c>
       <c r="C6" t="n">
-        <v>132.3071928582299</v>
+        <v>135.8895902310265</v>
       </c>
       <c r="D6" t="n">
-        <v>43.06927178530758</v>
+        <v>53.85671555957153</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.9794497181356</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="C7" t="n">
-        <v>99.2919993121139</v>
+        <v>125.1630148144258</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.93867397844697</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>62.33607048115122</v>
+        <v>84.19959185472769</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.692295639146882</v>
+        <v>7.650904841713457</v>
       </c>
       <c r="C21" t="n">
-        <v>94.23062157954929</v>
+        <v>92.76722120577566</v>
       </c>
       <c r="D21" t="n">
-        <v>8.653832594040242</v>
+        <v>7.650904841713457</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.178940124080178</v>
+        <v>6.376451339083034</v>
       </c>
       <c r="C2" t="n">
-        <v>12.46328710541326</v>
+        <v>11.47761241034946</v>
       </c>
       <c r="D2" t="n">
-        <v>20.47336662436298</v>
+        <v>34.06173659884308</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>17.50947030524186</v>
       </c>
       <c r="C3" t="n">
-        <v>36.21667280966484</v>
+        <v>26.07521902479529</v>
       </c>
       <c r="D3" t="n">
-        <v>61.01561981893926</v>
+        <v>94.50303401079798</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.72285371442869</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="C4" t="n">
-        <v>93.0147044911598</v>
+        <v>50.06815116888308</v>
       </c>
       <c r="D4" t="n">
-        <v>86.00797112595031</v>
+        <v>136.1654613359198</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.23526926278331</v>
+        <v>44.42408361716817</v>
       </c>
       <c r="C5" t="n">
-        <v>169.1060420565131</v>
+        <v>105.1697228174396</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59332943739291</v>
+        <v>108.6058397823034</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.90325861229863</v>
+        <v>45.04160292313942</v>
       </c>
       <c r="C6" t="n">
-        <v>178.91861036046</v>
+        <v>149.9776697869682</v>
       </c>
       <c r="D6" t="n">
-        <v>50.07305990740432</v>
+        <v>65.69070238656259</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.16017341117502</v>
+        <v>33.0574086973986</v>
       </c>
       <c r="C7" t="n">
-        <v>142.2306986527566</v>
+        <v>158.2803101217835</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>19.27661617288612</v>
       </c>
       <c r="C8" t="n">
-        <v>93.71272710887928</v>
+        <v>120.4162646643925</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>9.762499171030278</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>36.01541453029424</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.869702738002739</v>
+        <v>7.823808261509558</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3061355940356</v>
+        <v>100.7315313669356</v>
       </c>
       <c r="D21" t="n">
-        <v>9.837128422503424</v>
+        <v>8.801784294198253</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.076838362838508</v>
+        <v>6.736752746541613</v>
       </c>
       <c r="C2" t="n">
-        <v>10.50764567855361</v>
+        <v>11.74366603820035</v>
       </c>
       <c r="D2" t="n">
-        <v>31.29615331597982</v>
+        <v>39.20314932598363</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.67208057124834</v>
+        <v>18.83482970597506</v>
       </c>
       <c r="C3" t="n">
-        <v>41.90099201725387</v>
+        <v>34.21390749300134</v>
       </c>
       <c r="D3" t="n">
-        <v>62.07099860100459</v>
+        <v>97.55136063248432</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.089225534562</v>
+        <v>31.76641046631405</v>
       </c>
       <c r="C4" t="n">
-        <v>90.66636398260144</v>
+        <v>56.02834148136547</v>
       </c>
       <c r="D4" t="n">
-        <v>93.0147044911598</v>
+        <v>146.4905019414836</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.03891972193394</v>
+        <v>45.11130701014094</v>
       </c>
       <c r="C5" t="n">
-        <v>167.9770321966293</v>
+        <v>99.30378028456489</v>
       </c>
       <c r="D5" t="n">
-        <v>79.61973881441634</v>
+        <v>127.3572209334175</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.70578845502478</v>
+        <v>50.75733805726436</v>
       </c>
       <c r="C6" t="n">
-        <v>216.9966768173768</v>
+        <v>156.0556698239603</v>
       </c>
       <c r="D6" t="n">
-        <v>57.07684802950107</v>
+        <v>79.29576207201488</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.10135066437822</v>
+        <v>41.20198765183014</v>
       </c>
       <c r="C7" t="n">
-        <v>189.3614606905333</v>
+        <v>182.0552942755285</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>52.16123727433727</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.87873061522568</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="C8" t="n">
-        <v>132.6832022289564</v>
+        <v>158.6357027907208</v>
       </c>
       <c r="D8" t="n">
-        <v>40.13875488813084</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.75156107756332</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>81.09530561389926</v>
+        <v>103.6156162016168</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>47.97310156802039</v>
+        <v>60.07314202286233</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>36.25005223160922</v>
+        <v>39.44858625204532</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.029811082250669</v>
+        <v>7.981389543441924</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4099023809467</v>
+        <v>107.748758836466</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04099023809467</v>
+        <v>9.976736929302405</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.467173038501239</v>
+        <v>6.262568605390403</v>
       </c>
       <c r="C2" t="n">
-        <v>7.313038648934491</v>
+        <v>8.173049637854696</v>
       </c>
       <c r="D2" t="n">
-        <v>25.63245081017997</v>
+        <v>32.29851772201582</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.64677611511618</v>
+        <v>22.12368451520187</v>
       </c>
       <c r="C3" t="n">
-        <v>60.41675371934871</v>
+        <v>48.05164138436013</v>
       </c>
       <c r="D3" t="n">
-        <v>67.59823817591413</v>
+        <v>106.2741889847172</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.47438942979624</v>
+        <v>21.67109882354409</v>
       </c>
       <c r="C4" t="n">
-        <v>132.5918996924615</v>
+        <v>79.69042464912209</v>
       </c>
       <c r="D4" t="n">
-        <v>89.32627836630454</v>
+        <v>141.3981765995553</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.7538687303371</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>129.6643280383975</v>
+        <v>93.24148821084083</v>
       </c>
       <c r="D5" t="n">
-        <v>55.49328898255097</v>
+        <v>81.60777791551612</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.32207966691774</v>
+        <v>25.55980148006571</v>
       </c>
       <c r="C6" t="n">
-        <v>124.6996298980214</v>
+        <v>119.9096828490012</v>
       </c>
       <c r="D6" t="n">
-        <v>30.10823859384119</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>17.12757044828985</v>
       </c>
       <c r="C7" t="n">
-        <v>93.30333831620835</v>
+        <v>111.5088677437612</v>
       </c>
       <c r="D7" t="n">
-        <v>28.20659329071511</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>59.74916528046088</v>
+        <v>76.35542769779568</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>26.8704346652352</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>28.32833000604172</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.575926049494383</v>
+        <v>3.799363615435156</v>
       </c>
       <c r="C2" t="n">
-        <v>3.728677780729386</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="D2" t="n">
-        <v>18.03863231783089</v>
+        <v>21.98918507972006</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.80523840612741</v>
+        <v>22.39857387239098</v>
       </c>
       <c r="C3" t="n">
-        <v>45.0769458404923</v>
+        <v>40.79161711145497</v>
       </c>
       <c r="D3" t="n">
-        <v>72.58551651348793</v>
+        <v>108.6794708601219</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.04642954620264</v>
+        <v>30.19659588722339</v>
       </c>
       <c r="C4" t="n">
-        <v>146.209722098069</v>
+        <v>101.5019133943735</v>
       </c>
       <c r="D4" t="n">
-        <v>99.90657337497241</v>
+        <v>157.8748483199296</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.94454876913922</v>
+        <v>31.75953823238432</v>
       </c>
       <c r="C5" t="n">
-        <v>183.7095391571844</v>
+        <v>118.49694790259</v>
       </c>
       <c r="D5" t="n">
-        <v>69.36047530503717</v>
+        <v>105.2188102026519</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>30.06798693796707</v>
       </c>
       <c r="C6" t="n">
-        <v>160.6443585936099</v>
+        <v>138.3046895834737</v>
       </c>
       <c r="D6" t="n">
-        <v>36.46800022195202</v>
+        <v>43.51203999992289</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>125.8816541339345</v>
+        <v>137.200223416196</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>79.27612711792993</v>
+        <v>100.7224057172015</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.334416114249668</v>
+        <v>4.570035563268902</v>
       </c>
       <c r="C2" t="n">
-        <v>7.222717860143783</v>
+        <v>10.57636801785089</v>
       </c>
       <c r="D2" t="n">
-        <v>18.26541603751191</v>
+        <v>20.48711109222244</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.65597169735289</v>
+        <v>17.82853830912208</v>
       </c>
       <c r="C3" t="n">
-        <v>29.24135537099124</v>
+        <v>28.21542902005333</v>
       </c>
       <c r="D3" t="n">
-        <v>70.10169482174349</v>
+        <v>101.5470737887688</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.93829843001524</v>
+        <v>35.78666731520473</v>
       </c>
       <c r="C4" t="n">
-        <v>129.2353042916416</v>
+        <v>101.5657269951495</v>
       </c>
       <c r="D4" t="n">
-        <v>111.3547333541945</v>
+        <v>173.4198414689736</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.59588946541137</v>
+        <v>37.87091769132071</v>
       </c>
       <c r="C5" t="n">
-        <v>224.7956805799135</v>
+        <v>152.4899621621358</v>
       </c>
       <c r="D5" t="n">
-        <v>86.09927366244528</v>
+        <v>132.4868526881071</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.19631814978292</v>
+        <v>35.70321876034376</v>
       </c>
       <c r="C6" t="n">
-        <v>222.7526636073758</v>
+        <v>161.2078817758475</v>
       </c>
       <c r="D6" t="n">
-        <v>47.0944373727195</v>
+        <v>61.50453017565419</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>23.89475737366311</v>
       </c>
       <c r="C7" t="n">
-        <v>174.6892412505647</v>
+        <v>167.3830748355599</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>11.34900346109313</v>
       </c>
       <c r="C8" t="n">
-        <v>117.6624623539802</v>
+        <v>137.1059756365883</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>80.54061816099981</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14718970684157</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.63954402828795</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.623229865747478</v>
+        <v>2.724349879284899</v>
       </c>
       <c r="C2" t="n">
-        <v>3.45967890976576</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7578114166873</v>
+        <v>14.27362987204438</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.33690369347268</v>
+        <v>18.32922963828795</v>
       </c>
       <c r="C3" t="n">
-        <v>30.65016332658542</v>
+        <v>35.4901795085222</v>
       </c>
       <c r="D3" t="n">
-        <v>70.73492209098269</v>
+        <v>99.36268514681967</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.71606359595697</v>
+        <v>39.43680527959437</v>
       </c>
       <c r="C4" t="n">
-        <v>122.0881810047248</v>
+        <v>100.2639295393183</v>
       </c>
       <c r="D4" t="n">
-        <v>119.8674676977186</v>
+        <v>184.9573404892821</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.73119072214818</v>
+        <v>39.09810232162923</v>
       </c>
       <c r="C5" t="n">
-        <v>266.5690453956153</v>
+        <v>186.6302385773187</v>
       </c>
       <c r="D5" t="n">
-        <v>91.08164326149785</v>
+        <v>139.5554361586841</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>29.02144388523996</v>
       </c>
       <c r="C6" t="n">
-        <v>256.2822929505172</v>
+        <v>192.8859349487794</v>
       </c>
       <c r="D6" t="n">
-        <v>46.61141750223008</v>
+        <v>59.4516957260741</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>7.485826244881928</v>
       </c>
       <c r="C7" t="n">
-        <v>170.8564982131851</v>
+        <v>177.3841386987222</v>
       </c>
       <c r="D7" t="n">
-        <v>34.01559445674349</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>82.5306207575081</v>
+        <v>99.63757450400877</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.28437234352885</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>22.92282714645877</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.987458264023044</v>
+        <v>3.262347621212151</v>
       </c>
       <c r="C2" t="n">
-        <v>7.348381566287376</v>
+        <v>8.888743714250621</v>
       </c>
       <c r="D2" t="n">
-        <v>13.96536109291088</v>
+        <v>14.67614643078557</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93729132011522</v>
+        <v>14.03899217072939</v>
       </c>
       <c r="C3" t="n">
-        <v>22.07950586851076</v>
+        <v>27.58711048933537</v>
       </c>
       <c r="D3" t="n">
-        <v>65.20277377755191</v>
+        <v>89.26050127012</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.43604451606838</v>
+        <v>37.26714285320892</v>
       </c>
       <c r="C4" t="n">
-        <v>101.1828453904933</v>
+        <v>95.45238404080463</v>
       </c>
       <c r="D4" t="n">
-        <v>126.0573869729947</v>
+        <v>190.5984627978843</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.00870652728054</v>
+        <v>47.5411325781518</v>
       </c>
       <c r="C5" t="n">
-        <v>249.8302470382071</v>
+        <v>187.1947435072606</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3849465488479</v>
+        <v>166.4307795624406</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.81267578160067</v>
+        <v>38.19882142453915</v>
       </c>
       <c r="C6" t="n">
-        <v>329.4598033296659</v>
+        <v>238.692319333527</v>
       </c>
       <c r="D6" t="n">
-        <v>60.25672884355649</v>
+        <v>81.99262301558088</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>252.841267247132</v>
+        <v>220.9217041389555</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>139.7763293921396</v>
+        <v>153.5453409442011</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>54.58124536530566</v>
+        <v>65.34218195155493</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.08946221427348</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.34962535589888</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.264891953697392</v>
+        <v>2.148063976892021</v>
       </c>
       <c r="C2" t="n">
-        <v>4.163592013710723</v>
+        <v>5.083489612589984</v>
       </c>
       <c r="D2" t="n">
-        <v>9.88325413865264</v>
+        <v>11.91449013873929</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.09651437465245</v>
+        <v>12.92470852640926</v>
       </c>
       <c r="C3" t="n">
-        <v>25.35363446217388</v>
+        <v>30.91032646821083</v>
       </c>
       <c r="D3" t="n">
-        <v>62.27716561889642</v>
+        <v>82.76624020652736</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.14777054391831</v>
+        <v>34.10198825471721</v>
       </c>
       <c r="C4" t="n">
-        <v>84.20842758406592</v>
+        <v>86.8758360965045</v>
       </c>
       <c r="D4" t="n">
-        <v>128.8524226869854</v>
+        <v>191.7981584924739</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.64746442984672</v>
+        <v>51.46812339513905</v>
       </c>
       <c r="C5" t="n">
-        <v>235.1285751671111</v>
+        <v>189.2318699935727</v>
       </c>
       <c r="D5" t="n">
-        <v>121.3194725522996</v>
+        <v>185.6975782582842</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.69570893607505</v>
+        <v>44.80009298789471</v>
       </c>
       <c r="C6" t="n">
-        <v>366.5718300456039</v>
+        <v>268.5187963362494</v>
       </c>
       <c r="D6" t="n">
-        <v>69.71586797397451</v>
+        <v>97.28825224774619</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.72643654788041</v>
+        <v>14.25301317025519</v>
       </c>
       <c r="C7" t="n">
-        <v>323.5673536087765</v>
+        <v>264.0400633094754</v>
       </c>
       <c r="D7" t="n">
-        <v>41.74096714146164</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>183.5868206941535</v>
+        <v>194.1013386066369</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90468232835936</v>
+        <v>71.66561891460864</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.082687791334985</v>
+        <v>2.373865948868787</v>
       </c>
       <c r="C2" t="n">
-        <v>6.612070788102268</v>
+        <v>7.689048019661019</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1110196060379</v>
+        <v>13.67083678163683</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.53415286656828</v>
+        <v>10.2494460323367</v>
       </c>
       <c r="C3" t="n">
-        <v>21.27447275102838</v>
+        <v>25.65306751196916</v>
       </c>
       <c r="D3" t="n">
-        <v>57.3438834050562</v>
+        <v>75.47676350249479</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.95785126864217</v>
+        <v>29.77542612210151</v>
       </c>
       <c r="C4" t="n">
-        <v>75.0703199529366</v>
+        <v>82.37059588171589</v>
       </c>
       <c r="D4" t="n">
-        <v>128.1377103582937</v>
+        <v>187.2673928373748</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.22393025868885</v>
+        <v>51.14905539125883</v>
       </c>
       <c r="C5" t="n">
-        <v>202.1173086118121</v>
+        <v>176.5673246087889</v>
       </c>
       <c r="D5" t="n">
-        <v>134.6221539448439</v>
+        <v>204.6453089502477</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.75862290460487</v>
+        <v>53.61520562432682</v>
       </c>
       <c r="C6" t="n">
-        <v>370.5567439771417</v>
+        <v>281.9628493982052</v>
       </c>
       <c r="D6" t="n">
-        <v>84.93099389439158</v>
+        <v>121.882013986833</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.33876937788993</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>401.6594929953848</v>
+        <v>315.6024344842221</v>
       </c>
       <c r="D7" t="n">
-        <v>48.56804067679396</v>
+        <v>57.43125895073415</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>272.542980175957</v>
+        <v>251.9311871252953</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>118.8140524110617</v>
+        <v>130.6843639031099</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>48.9695754878309</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3725,7 +3725,7 @@
         <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.750096303773569</v>
+        <v>4.767366851822511</v>
       </c>
       <c r="C2" t="n">
-        <v>5.254313713128929</v>
+        <v>10.53611636197677</v>
       </c>
       <c r="D2" t="n">
-        <v>8.898561191293089</v>
+        <v>11.52866329097029</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.255074476654924</v>
+        <v>1.717076734727671</v>
       </c>
       <c r="C2" t="n">
-        <v>3.861213720802705</v>
+        <v>4.489532251520663</v>
       </c>
       <c r="D2" t="n">
-        <v>7.522150909939061</v>
+        <v>10.17090621599696</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.16661937228147</v>
+        <v>13.48430471782994</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00158794697677</v>
+        <v>30.71397692736146</v>
       </c>
       <c r="D3" t="n">
-        <v>61.66357330374216</v>
+        <v>81.12181280191395</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.77162230447154</v>
+        <v>39.55166976099125</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4230547828642</v>
+        <v>114.8006677961008</v>
       </c>
       <c r="D4" t="n">
-        <v>129.9627793404885</v>
+        <v>192.7298370638041</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.44738352016284</v>
+        <v>31.14594591723007</v>
       </c>
       <c r="C5" t="n">
-        <v>309.6186822268378</v>
+        <v>250.0265965790565</v>
       </c>
       <c r="D5" t="n">
-        <v>122.7920941086698</v>
+        <v>184.4703936279757</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.04532462531138</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="C6" t="n">
-        <v>329.9025715442813</v>
+        <v>257.6105975943631</v>
       </c>
       <c r="D6" t="n">
-        <v>68.58882160949918</v>
+        <v>91.41151049012478</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>191.6371518689774</v>
+        <v>177.144592258886</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>87.53753404916685</v>
+        <v>96.29963230956963</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4333,7 +4333,7 @@
         <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.969426952448107</v>
+        <v>6.528622233241289</v>
       </c>
       <c r="C2" t="n">
-        <v>3.723769042208152</v>
+        <v>5.85710680353647</v>
       </c>
       <c r="D2" t="n">
-        <v>13.77686553369549</v>
+        <v>23.35675963173586</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.21294144083032</v>
+        <v>10.13163630782708</v>
       </c>
       <c r="C3" t="n">
-        <v>13.23886779176824</v>
+        <v>26.54645792283375</v>
       </c>
       <c r="D3" t="n">
-        <v>10.61269268290802</v>
+        <v>12.82162501746335</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39858547810929</v>
+        <v>13.39739606047418</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14553573833687</v>
+        <v>70.13930878718834</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57630417389521</v>
+        <v>1.576164242408727</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.266495596207391</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C2" t="n">
-        <v>9.63094497866121</v>
+        <v>5.633268326968198</v>
       </c>
       <c r="D2" t="n">
-        <v>14.03801042302514</v>
+        <v>36.04977569994288</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.31588608105599</v>
+        <v>17.5438314748905</v>
       </c>
       <c r="C3" t="n">
-        <v>14.06353586333556</v>
+        <v>24.22953334081128</v>
       </c>
       <c r="D3" t="n">
-        <v>19.62022786937251</v>
+        <v>29.33953014141593</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.21767025290231</v>
+        <v>11.88209246449915</v>
       </c>
       <c r="C4" t="n">
-        <v>21.04572553593887</v>
+        <v>40.99385713852982</v>
       </c>
       <c r="D4" t="n">
-        <v>20.6373184909722</v>
+        <v>21.78596330494097</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44335744199939</v>
+        <v>15.43734185843956</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1576783606282</v>
+        <v>86.12411773655752</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251233145684083</v>
+        <v>3.249966707039907</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.754023294590556</v>
+        <v>4.112541133089889</v>
       </c>
       <c r="C2" t="n">
-        <v>4.929355223023235</v>
+        <v>8.59029241215959</v>
       </c>
       <c r="D2" t="n">
-        <v>14.4356182432451</v>
+        <v>36.14009648873358</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.67069791291659</v>
+        <v>15.96812640957437</v>
       </c>
       <c r="C3" t="n">
-        <v>28.25960766674444</v>
+        <v>22.83545160078081</v>
       </c>
       <c r="D3" t="n">
-        <v>26.29611225825082</v>
+        <v>51.36994862471436</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.26117025152543</v>
+        <v>24.01943933210246</v>
       </c>
       <c r="C4" t="n">
-        <v>29.39254451744526</v>
+        <v>52.39096623713103</v>
       </c>
       <c r="D4" t="n">
-        <v>25.83174559414208</v>
+        <v>31.57496966398591</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.68908907739003</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="C5" t="n">
-        <v>24.42097414313941</v>
+        <v>44.74315162104839</v>
       </c>
       <c r="D5" t="n">
-        <v>29.86967390170921</v>
+        <v>30.77779052813751</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74015719948235</v>
+        <v>16.72360921872659</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1149589168423</v>
+        <v>102.0140162342322</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022047159844703</v>
+        <v>4.180902304681647</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.670574739729576</v>
+        <v>5.795256698168921</v>
       </c>
       <c r="C2" t="n">
-        <v>12.2335581426195</v>
+        <v>7.256097282088176</v>
       </c>
       <c r="D2" t="n">
-        <v>21.01529135710722</v>
+        <v>32.15616430490002</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.15037162966578</v>
+        <v>14.91274762750905</v>
       </c>
       <c r="C3" t="n">
-        <v>22.90417394007808</v>
+        <v>28.76029899591031</v>
       </c>
       <c r="D3" t="n">
-        <v>31.41592653589793</v>
+        <v>67.41170611210724</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.05093737409637</v>
+        <v>27.72062817711294</v>
       </c>
       <c r="C4" t="n">
-        <v>52.90147504333937</v>
+        <v>54.98179842863836</v>
       </c>
       <c r="D4" t="n">
-        <v>32.54493639578177</v>
+        <v>49.21304891848411</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.09623663721197</v>
+        <v>22.9483525867692</v>
       </c>
       <c r="C5" t="n">
-        <v>40.84070449666732</v>
+        <v>71.86393195086653</v>
       </c>
       <c r="D5" t="n">
-        <v>32.56948008838794</v>
+        <v>34.9993056563988</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>26.08307300642926</v>
+        <v>42.62650357069227</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>37.59504658642736</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07137190744526</v>
+        <v>18.03764300233637</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8941881580952</v>
+        <v>117.6741472057182</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884332155217241</v>
+        <v>6.012547667445455</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.637596228412685</v>
+        <v>6.105488972710914</v>
       </c>
       <c r="C2" t="n">
-        <v>14.45525319733004</v>
+        <v>6.021058670145687</v>
       </c>
       <c r="D2" t="n">
-        <v>23.96446146066464</v>
+        <v>31.87342096607695</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.78926840095221</v>
+        <v>15.62942345160922</v>
       </c>
       <c r="C3" t="n">
-        <v>34.77841242294325</v>
+        <v>26.66426764734337</v>
       </c>
       <c r="D3" t="n">
-        <v>38.00345363139403</v>
+        <v>72.31062715629882</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.63579696392021</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="C4" t="n">
-        <v>45.93302983859552</v>
+        <v>53.74381457358314</v>
       </c>
       <c r="D4" t="n">
-        <v>35.05919226635785</v>
+        <v>61.73327739074368</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.00373136883452</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>53.48070618884501</v>
+        <v>64.45173678380311</v>
       </c>
       <c r="D5" t="n">
-        <v>30.0414797499524</v>
+        <v>35.80924751240241</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.32329809433347</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>31.27553661419064</v>
+        <v>53.73596059194917</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>30.71201343195298</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>19.16371518689774</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.77592484372025</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064670597463668</v>
+        <v>7.044587463912031</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23128685122188</v>
+        <v>66.04300747417528</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298502948097751</v>
+        <v>4.402867164945019</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.791329707351935</v>
+        <v>4.625013434706723</v>
       </c>
       <c r="C2" t="n">
-        <v>9.718320524339175</v>
+        <v>4.610287219143022</v>
       </c>
       <c r="D2" t="n">
-        <v>25.62852381936299</v>
+        <v>33.65136605846792</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.1910241961674</v>
+        <v>19.22262004915255</v>
       </c>
       <c r="C3" t="n">
-        <v>49.02357161156448</v>
+        <v>24.65659359215864</v>
       </c>
       <c r="D3" t="n">
-        <v>49.54389789481529</v>
+        <v>81.61268665403736</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.9961394291078</v>
+        <v>26.34225440035042</v>
       </c>
       <c r="C4" t="n">
-        <v>72.30080967925635</v>
+        <v>61.89919275276139</v>
       </c>
       <c r="D4" t="n">
-        <v>47.45179353706533</v>
+        <v>85.30602151741385</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.33033455917922</v>
+        <v>26.21266370338984</v>
       </c>
       <c r="C5" t="n">
-        <v>73.09111658117504</v>
+        <v>85.51022503989719</v>
       </c>
       <c r="D5" t="n">
-        <v>36.64373306101221</v>
+        <v>50.29002615004288</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.55351008321273</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>63.35610634586367</v>
+        <v>81.99262301558088</v>
       </c>
       <c r="D6" t="n">
-        <v>33.81139093426016</v>
+        <v>35.62271544859552</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.49822911213864</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>34.6743471662931</v>
+        <v>55.75443387188061</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11524969649115</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
         <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288684520013784</v>
+        <v>7.260494000491232</v>
       </c>
       <c r="C21" t="n">
-        <v>75.62010189514302</v>
+        <v>75.32762525509654</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377598955012061</v>
+        <v>5.445370500368424</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.511130701014094</v>
+        <v>4.547455366071226</v>
       </c>
       <c r="C2" t="n">
-        <v>6.939974521320702</v>
+        <v>4.005530633326987</v>
       </c>
       <c r="D2" t="n">
-        <v>20.10619298297468</v>
+        <v>29.36701907713484</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.55779692692821</v>
+        <v>17.39166058073225</v>
       </c>
       <c r="C3" t="n">
-        <v>42.22987749817655</v>
+        <v>20.6854241284803</v>
       </c>
       <c r="D3" t="n">
-        <v>58.55143308127977</v>
+        <v>89.03469929814324</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.44582093538184</v>
+        <v>32.55769911593697</v>
       </c>
       <c r="C4" t="n">
-        <v>102.0379476408922</v>
+        <v>61.80985371167493</v>
       </c>
       <c r="D4" t="n">
-        <v>61.61841290934681</v>
+        <v>105.0371868773663</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.25794727097221</v>
+        <v>33.15852871093603</v>
       </c>
       <c r="C5" t="n">
-        <v>107.6486357706628</v>
+        <v>100.6045959926919</v>
       </c>
       <c r="D5" t="n">
-        <v>45.13585070274711</v>
+        <v>69.50773746067419</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.90447703971436</v>
+        <v>28.29691407950582</v>
       </c>
       <c r="C6" t="n">
-        <v>91.81402704886597</v>
+        <v>111.2555768360656</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>42.86801350593698</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.90042687571034</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>66.17470400475625</v>
+        <v>89.47059527882881</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>35.88287859022092</v>
+        <v>51.98844967838984</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>26.95781021091316</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.498279079663164</v>
+        <v>7.462706731903255</v>
       </c>
       <c r="C21" t="n">
-        <v>85.2929245311685</v>
+        <v>83.95545073391162</v>
       </c>
       <c r="D21" t="n">
-        <v>7.498279079663164</v>
+        <v>6.529868390415349</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_3_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497635390578</v>
+        <v>10.84497641201189</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907201749033</v>
+        <v>37.78907221995971</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.737333583618359</v>
+        <v>8.055239913345078</v>
       </c>
       <c r="C2" t="n">
-        <v>8.948630324209677</v>
+        <v>12.22766765639402</v>
       </c>
       <c r="D2" t="n">
-        <v>32.71281525320797</v>
+        <v>24.65855708756714</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.29701189049705</v>
+        <v>23.04161861867264</v>
       </c>
       <c r="C3" t="n">
-        <v>17.82362957060084</v>
+        <v>26.96370069713865</v>
       </c>
       <c r="D3" t="n">
-        <v>91.22890541713485</v>
+        <v>76.77267047210057</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.76190263842031</v>
+        <v>41.98934931063608</v>
       </c>
       <c r="C4" t="n">
-        <v>56.43674852633215</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6835210241259</v>
+        <v>89.14760028413161</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.01251034491051</v>
+        <v>50.53546307610458</v>
       </c>
       <c r="C5" t="n">
-        <v>106.4705385255666</v>
+        <v>70.36676670189014</v>
       </c>
       <c r="D5" t="n">
-        <v>88.33274968960677</v>
+        <v>63.17546476828226</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>48.94601354292898</v>
       </c>
       <c r="C6" t="n">
-        <v>135.8895902310265</v>
+        <v>77.32343093418305</v>
       </c>
       <c r="D6" t="n">
-        <v>53.85671555957153</v>
+        <v>44.03531152628644</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>37.78845088416398</v>
       </c>
       <c r="C7" t="n">
-        <v>125.1630148144258</v>
+        <v>63.24026011676253</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="C8" t="n">
-        <v>84.19959185472769</v>
+        <v>40.80634332701867</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>9.207811718130833</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.650904841713457</v>
+        <v>7.724790897824544</v>
       </c>
       <c r="C21" t="n">
-        <v>92.76722120577566</v>
+        <v>96.55988622280681</v>
       </c>
       <c r="D21" t="n">
-        <v>7.650904841713457</v>
+        <v>8.690389760052613</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.376451339083034</v>
+        <v>10.59403947652733</v>
       </c>
       <c r="C2" t="n">
-        <v>11.47761241034946</v>
+        <v>13.65611056607313</v>
       </c>
       <c r="D2" t="n">
-        <v>34.06173659884308</v>
+        <v>30.63347361561323</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.50947030524186</v>
+        <v>25.16710239836699</v>
       </c>
       <c r="C3" t="n">
-        <v>26.07521902479529</v>
+        <v>38.34706532788041</v>
       </c>
       <c r="D3" t="n">
-        <v>94.50303401079798</v>
+        <v>78.18638716621598</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.46010518258904</v>
+        <v>43.20180772538089</v>
       </c>
       <c r="C4" t="n">
-        <v>50.06815116888308</v>
+        <v>57.80235958293945</v>
       </c>
       <c r="D4" t="n">
-        <v>136.1654613359198</v>
+        <v>105.5221702432642</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.42408361716817</v>
+        <v>56.42594930158544</v>
       </c>
       <c r="C5" t="n">
-        <v>105.1697228174396</v>
+        <v>80.11061266653974</v>
       </c>
       <c r="D5" t="n">
-        <v>108.6058397823034</v>
+        <v>78.29437941368315</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.04160292313942</v>
+        <v>58.52590764096936</v>
       </c>
       <c r="C6" t="n">
-        <v>149.9776697869682</v>
+        <v>93.66560321907546</v>
       </c>
       <c r="D6" t="n">
-        <v>65.69070238656259</v>
+        <v>53.13218575383738</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.0574086973986</v>
+        <v>48.50815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>158.2803101217835</v>
+        <v>87.55422376013904</v>
       </c>
       <c r="D7" t="n">
-        <v>45.51382356888213</v>
+        <v>42.75903951076558</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.27661617288612</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="C8" t="n">
-        <v>120.4162646643925</v>
+        <v>61.66848204226339</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.762499171030278</v>
+        <v>14.75468624712531</v>
       </c>
       <c r="C9" t="n">
-        <v>72.66405632982764</v>
+        <v>40.71405904281946</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.823808261509558</v>
+        <v>7.9165501808131</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7315313669356</v>
+        <v>105.8838586683752</v>
       </c>
       <c r="D21" t="n">
-        <v>8.801784294198253</v>
+        <v>9.895687726016375</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.736752746541613</v>
+        <v>11.1428364432013</v>
       </c>
       <c r="C2" t="n">
-        <v>11.74366603820035</v>
+        <v>9.389435043416494</v>
       </c>
       <c r="D2" t="n">
-        <v>39.20314932598363</v>
+        <v>40.0435253608189</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.83482970597506</v>
+        <v>29.81567777797563</v>
       </c>
       <c r="C3" t="n">
-        <v>34.21390749300134</v>
+        <v>45.36165267472387</v>
       </c>
       <c r="D3" t="n">
-        <v>97.55136063248432</v>
+        <v>82.65333922053897</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.76641046631405</v>
+        <v>44.74609686416112</v>
       </c>
       <c r="C4" t="n">
-        <v>56.02834148136547</v>
+        <v>75.89989676302515</v>
       </c>
       <c r="D4" t="n">
-        <v>146.4905019414836</v>
+        <v>116.3066687744154</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.11130701014094</v>
+        <v>60.45111488899736</v>
       </c>
       <c r="C5" t="n">
-        <v>99.30378028456489</v>
+        <v>91.37616757277189</v>
       </c>
       <c r="D5" t="n">
-        <v>127.3572209334175</v>
+        <v>95.05772146369743</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.75733805726436</v>
+        <v>66.21397391292614</v>
       </c>
       <c r="C6" t="n">
-        <v>156.0556698239603</v>
+        <v>108.1561993337584</v>
       </c>
       <c r="D6" t="n">
-        <v>79.29576207201488</v>
+        <v>62.71207985187777</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.20198765183014</v>
+        <v>58.09001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>182.0552942755285</v>
+        <v>109.8320426649077</v>
       </c>
       <c r="D7" t="n">
-        <v>52.16123727433727</v>
+        <v>47.60985491744906</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.86905200690345</v>
+        <v>40.3056519978528</v>
       </c>
       <c r="C8" t="n">
-        <v>158.6357027907208</v>
+        <v>85.86856295194725</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>40.88979188187965</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="C9" t="n">
-        <v>103.6156162016168</v>
+        <v>57.243745139223</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>39.44858625204532</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.981389543441924</v>
+        <v>8.09199337320149</v>
       </c>
       <c r="C21" t="n">
-        <v>107.748758836466</v>
+        <v>114.299406396471</v>
       </c>
       <c r="D21" t="n">
-        <v>9.976736929302405</v>
+        <v>11.12649088815205</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.262568605390403</v>
+        <v>10.14734427109503</v>
       </c>
       <c r="C2" t="n">
-        <v>8.173049637854696</v>
+        <v>6.234097921967246</v>
       </c>
       <c r="D2" t="n">
-        <v>32.29851772201582</v>
+        <v>32.3485868549324</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.12368451520187</v>
+        <v>33.96847056693964</v>
       </c>
       <c r="C3" t="n">
-        <v>48.05164138436013</v>
+        <v>61.13833828197012</v>
       </c>
       <c r="D3" t="n">
-        <v>106.2741889847172</v>
+        <v>91.08655200001907</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.67109882354409</v>
+        <v>29.03518835309942</v>
       </c>
       <c r="C4" t="n">
-        <v>79.69042464912209</v>
+        <v>89.32627836630454</v>
       </c>
       <c r="D4" t="n">
-        <v>141.3981765995553</v>
+        <v>110.7293600665893</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>37.28186906877263</v>
       </c>
       <c r="C5" t="n">
-        <v>93.24148821084083</v>
+        <v>64.62354263204631</v>
       </c>
       <c r="D5" t="n">
-        <v>81.60777791551612</v>
+        <v>63.93631923907354</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.55980148006571</v>
+        <v>36.06548366321083</v>
       </c>
       <c r="C6" t="n">
-        <v>119.9096828490012</v>
+        <v>72.33222560579226</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>31.35603992593888</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="C7" t="n">
-        <v>111.5088677437612</v>
+        <v>60.36570283872788</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>28.7455727803466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C8" t="n">
-        <v>76.35542769779568</v>
+        <v>42.14152020479433</v>
       </c>
       <c r="D8" t="n">
-        <v>26.8704346652352</v>
+        <v>27.62147165898401</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.799363615435156</v>
+        <v>6.115306449753382</v>
       </c>
       <c r="C2" t="n">
-        <v>4.319689898685966</v>
+        <v>2.728276870101886</v>
       </c>
       <c r="D2" t="n">
-        <v>21.98918507972006</v>
+        <v>21.84094117637879</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.39857387239098</v>
+        <v>35.56871932486194</v>
       </c>
       <c r="C3" t="n">
-        <v>40.79161711145497</v>
+        <v>42.55876297909924</v>
       </c>
       <c r="D3" t="n">
-        <v>108.6794708601219</v>
+        <v>96.7414187764807</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.19659588722339</v>
+        <v>45.38423287192155</v>
       </c>
       <c r="C4" t="n">
-        <v>101.5019133943735</v>
+        <v>124.3216570318863</v>
       </c>
       <c r="D4" t="n">
-        <v>157.8748483199296</v>
+        <v>128.8524226869854</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.75953823238432</v>
+        <v>41.62610266006477</v>
       </c>
       <c r="C5" t="n">
-        <v>118.49694790259</v>
+        <v>111.6247139728624</v>
       </c>
       <c r="D5" t="n">
-        <v>105.2188102026519</v>
+        <v>81.80412745636549</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.06798693796707</v>
+        <v>43.43153668817465</v>
       </c>
       <c r="C6" t="n">
-        <v>138.3046895834737</v>
+        <v>87.94986808495052</v>
       </c>
       <c r="D6" t="n">
-        <v>43.51203999992289</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>137.200223416196</v>
+        <v>79.05032514595315</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>100.7224057172015</v>
+        <v>55.40984042768998</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>28.87319998189869</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>49.58905828921062</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.570035563268902</v>
+        <v>6.813329067472864</v>
       </c>
       <c r="C2" t="n">
-        <v>10.57636801785089</v>
+        <v>3.849432748351743</v>
       </c>
       <c r="D2" t="n">
-        <v>20.48711109222244</v>
+        <v>19.04786895779661</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>28.03380569476767</v>
       </c>
       <c r="C3" t="n">
-        <v>28.21542902005333</v>
+        <v>24.98547907308132</v>
       </c>
       <c r="D3" t="n">
-        <v>101.5470737887688</v>
+        <v>91.87685890193775</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.78666731520473</v>
+        <v>57.07488453409257</v>
       </c>
       <c r="C4" t="n">
-        <v>101.5657269951495</v>
+        <v>115.9620753302247</v>
       </c>
       <c r="D4" t="n">
-        <v>173.4198414689736</v>
+        <v>146.1331457771377</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>53.97158004096841</v>
       </c>
       <c r="C5" t="n">
-        <v>152.4899621621358</v>
+        <v>170.4804888424586</v>
       </c>
       <c r="D5" t="n">
-        <v>132.4868526881071</v>
+        <v>106.3969074477481</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.70321876034376</v>
+        <v>49.79129831628549</v>
       </c>
       <c r="C6" t="n">
-        <v>161.2078817758475</v>
+        <v>131.7436696759922</v>
       </c>
       <c r="D6" t="n">
-        <v>61.50453017565419</v>
+        <v>53.01143078621504</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>36.77037851486003</v>
       </c>
       <c r="C7" t="n">
-        <v>167.3830748355599</v>
+        <v>102.585762859862</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C8" t="n">
-        <v>137.1059756365883</v>
+        <v>78.44164156932014</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>80.54061816099981</v>
+        <v>51.03124566674919</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>37.43894870145212</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.724349879284899</v>
+        <v>4.012402867256714</v>
       </c>
       <c r="C2" t="n">
-        <v>5.038329218194631</v>
+        <v>1.811324514335365</v>
       </c>
       <c r="D2" t="n">
-        <v>14.27362987204438</v>
+        <v>13.14462001216054</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32922963828795</v>
+        <v>28.47559216167874</v>
       </c>
       <c r="C3" t="n">
-        <v>35.4901795085222</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D3" t="n">
-        <v>99.36268514681967</v>
+        <v>90.04589943351745</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.43680527959437</v>
+        <v>62.86915948455724</v>
       </c>
       <c r="C4" t="n">
-        <v>100.2639295393183</v>
+        <v>107.5386800277871</v>
       </c>
       <c r="D4" t="n">
-        <v>184.9573404892821</v>
+        <v>157.6068311966702</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.09810232162923</v>
+        <v>55.81235698643118</v>
       </c>
       <c r="C5" t="n">
-        <v>186.6302385773187</v>
+        <v>204.5716778724292</v>
       </c>
       <c r="D5" t="n">
-        <v>139.5554361586841</v>
+        <v>116.4107340310656</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.02144388523996</v>
+        <v>43.51203999992289</v>
       </c>
       <c r="C6" t="n">
-        <v>192.8859349487794</v>
+        <v>163.6632327841688</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>51.72337779824321</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.485826244881928</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>177.3841386987222</v>
+        <v>106.8377121669549</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>99.63757450400877</v>
+        <v>62.16917337142927</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>30.22212132753381</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.262347621212151</v>
+        <v>5.548838024402973</v>
       </c>
       <c r="C2" t="n">
-        <v>8.888743714250621</v>
+        <v>2.811725424962865</v>
       </c>
       <c r="D2" t="n">
-        <v>14.67614643078557</v>
+        <v>17.0971362694582</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.03899217072939</v>
+        <v>21.29410770511332</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58711048933537</v>
+        <v>14.35315143608837</v>
       </c>
       <c r="D3" t="n">
-        <v>89.26050127012</v>
+        <v>80.68493507352412</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.26714285320892</v>
+        <v>59.5125640837374</v>
       </c>
       <c r="C4" t="n">
-        <v>95.45238404080463</v>
+        <v>82.42164676233671</v>
       </c>
       <c r="D4" t="n">
-        <v>190.5984627978843</v>
+        <v>165.2899887301057</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.5411325781518</v>
+        <v>72.1339125695344</v>
       </c>
       <c r="C5" t="n">
-        <v>187.1947435072606</v>
+        <v>201.3073667558085</v>
       </c>
       <c r="D5" t="n">
-        <v>166.4307795624406</v>
+        <v>142.6479414270616</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.19882142453915</v>
+        <v>55.99005332089985</v>
       </c>
       <c r="C6" t="n">
-        <v>238.692319333527</v>
+        <v>239.5376041068835</v>
       </c>
       <c r="D6" t="n">
-        <v>81.99262301558088</v>
+        <v>69.75611962984863</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>220.9217041389555</v>
+        <v>162.7119192587536</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>40.48334833232147</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>153.5453409442011</v>
+        <v>96.21618375470864</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>34.04701038327938</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>65.34218195155493</v>
+        <v>46.48280855297372</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.148063976892021</v>
+        <v>3.995713156284519</v>
       </c>
       <c r="C2" t="n">
-        <v>5.083489612589984</v>
+        <v>2.14217349066654</v>
       </c>
       <c r="D2" t="n">
-        <v>11.91449013873929</v>
+        <v>13.52848336452105</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.92470852640926</v>
+        <v>20.50380080319464</v>
       </c>
       <c r="C3" t="n">
-        <v>30.91032646821083</v>
+        <v>12.91489104936679</v>
       </c>
       <c r="D3" t="n">
-        <v>82.76624020652736</v>
+        <v>76.87084524252526</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.10198825471721</v>
+        <v>53.65447553249668</v>
       </c>
       <c r="C4" t="n">
-        <v>86.8758360965045</v>
+        <v>64.4517367838031</v>
       </c>
       <c r="D4" t="n">
-        <v>191.7981584924739</v>
+        <v>167.8297700409922</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.46812339513905</v>
+        <v>80.40513697781378</v>
       </c>
       <c r="C5" t="n">
         <v>189.2318699935727</v>
       </c>
       <c r="D5" t="n">
-        <v>185.6975782582842</v>
+        <v>161.2275167299325</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>66.65674212754145</v>
       </c>
       <c r="C6" t="n">
-        <v>268.5187963362494</v>
+        <v>277.4546639403039</v>
       </c>
       <c r="D6" t="n">
-        <v>97.28825224774619</v>
+        <v>84.44797402390215</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.25301317025519</v>
+        <v>23.71509754378595</v>
       </c>
       <c r="C7" t="n">
-        <v>264.0400633094754</v>
+        <v>221.2211371887508</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>46.05280305851362</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>194.1013386066369</v>
+        <v>126.424560614383</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>71.66561891460864</v>
+        <v>54.80312034646543</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.373865948868787</v>
+        <v>6.102543729598173</v>
       </c>
       <c r="C2" t="n">
-        <v>7.689048019661019</v>
+        <v>6.185010536754906</v>
       </c>
       <c r="D2" t="n">
-        <v>13.67083678163683</v>
+        <v>17.33373746618168</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.2494460323367</v>
+        <v>17.09222753093697</v>
       </c>
       <c r="C3" t="n">
-        <v>25.65306751196916</v>
+        <v>10.67159754516283</v>
       </c>
       <c r="D3" t="n">
-        <v>75.47676350249479</v>
+        <v>70.84291433844984</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.77542612210151</v>
+        <v>46.52011496573511</v>
       </c>
       <c r="C4" t="n">
-        <v>82.37059588171589</v>
+        <v>49.76184588515808</v>
       </c>
       <c r="D4" t="n">
-        <v>187.2673928373748</v>
+        <v>167.3320239549391</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.14905539125883</v>
+        <v>80.40513697781378</v>
       </c>
       <c r="C5" t="n">
-        <v>176.5673246087889</v>
+        <v>158.3313610024044</v>
       </c>
       <c r="D5" t="n">
-        <v>204.6453089502477</v>
+        <v>176.4691498383642</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.61520562432682</v>
+        <v>82.71715282131501</v>
       </c>
       <c r="C6" t="n">
-        <v>281.9628493982052</v>
+        <v>288.0005977793231</v>
       </c>
       <c r="D6" t="n">
-        <v>121.882013986833</v>
+        <v>107.5121728397725</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>42.75903951076558</v>
       </c>
       <c r="C7" t="n">
-        <v>315.6024344842221</v>
+        <v>296.4986059072834</v>
       </c>
       <c r="D7" t="n">
-        <v>57.43125895073415</v>
+        <v>55.69454726192155</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>251.9311871252953</v>
+        <v>190.5130507476148</v>
       </c>
       <c r="D8" t="n">
-        <v>37.1346069131356</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>130.6843639031099</v>
+        <v>92.96561710594743</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
         <v>26.62008900065227</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.87748682561417</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.767366851822511</v>
+        <v>8.305585577928015</v>
       </c>
       <c r="C2" t="n">
-        <v>10.53611636197677</v>
+        <v>2.836269117569035</v>
       </c>
       <c r="D2" t="n">
-        <v>11.52866329097029</v>
+        <v>7.536877125502762</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.717076734727671</v>
+        <v>4.367795536194059</v>
       </c>
       <c r="C2" t="n">
-        <v>4.489532251520663</v>
+        <v>3.513675033499335</v>
       </c>
       <c r="D2" t="n">
-        <v>10.17090621599696</v>
+        <v>12.7578114166873</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.48430471782994</v>
+        <v>22.88453898599315</v>
       </c>
       <c r="C3" t="n">
-        <v>30.71397692736146</v>
+        <v>16.29210315197582</v>
       </c>
       <c r="D3" t="n">
-        <v>81.12181280191395</v>
+        <v>77.87713663937824</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.55166976099125</v>
+        <v>62.43522699928015</v>
       </c>
       <c r="C4" t="n">
-        <v>114.8006677961008</v>
+        <v>75.98923580411162</v>
       </c>
       <c r="D4" t="n">
-        <v>192.7298370638041</v>
+        <v>170.5354667138965</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.14594591723007</v>
+        <v>48.81740459367266</v>
       </c>
       <c r="C5" t="n">
-        <v>250.0265965790565</v>
+        <v>241.019061392592</v>
       </c>
       <c r="D5" t="n">
-        <v>184.4703936279757</v>
+        <v>160.8593613408399</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.50317890838889</v>
+        <v>26.52584122104457</v>
       </c>
       <c r="C6" t="n">
-        <v>257.6105975943631</v>
+        <v>251.7338558367417</v>
       </c>
       <c r="D6" t="n">
-        <v>91.41151049012478</v>
+        <v>84.56872899152451</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.850815406683489</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>177.144592258886</v>
+        <v>133.966346478407</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>96.29963230956963</v>
+        <v>68.51126354086365</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>25.53525778745954</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
         <v>20.30156077611979</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.528622233241289</v>
+        <v>7.840237166115028</v>
       </c>
       <c r="C2" t="n">
-        <v>5.85710680353647</v>
+        <v>2.935425635697963</v>
       </c>
       <c r="D2" t="n">
-        <v>23.35675963173586</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.13163630782708</v>
+        <v>17.63218876827272</v>
       </c>
       <c r="C3" t="n">
-        <v>26.54645792283375</v>
+        <v>7.14712328691678</v>
       </c>
       <c r="D3" t="n">
-        <v>12.82162501746335</v>
+        <v>9.468956607460486</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39739606047418</v>
+        <v>13.39879599135628</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13930878718834</v>
+        <v>70.14663783710051</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576164242408727</v>
+        <v>1.576328940159562</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.270602513473626</v>
+        <v>4.824308218668826</v>
       </c>
       <c r="C2" t="n">
-        <v>5.633268326968198</v>
+        <v>3.319288988058466</v>
       </c>
       <c r="D2" t="n">
-        <v>36.04977569994288</v>
+        <v>18.23301836327176</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5438314748905</v>
+        <v>23.35086914551039</v>
       </c>
       <c r="C3" t="n">
-        <v>24.22953334081128</v>
+        <v>9.88619938176538</v>
       </c>
       <c r="D3" t="n">
-        <v>29.33953014141593</v>
+        <v>18.29977720716055</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.88209246449915</v>
+        <v>20.3437759274024</v>
       </c>
       <c r="C4" t="n">
-        <v>40.99385713852982</v>
+        <v>11.61407534123977</v>
       </c>
       <c r="D4" t="n">
-        <v>21.78596330494097</v>
+        <v>20.0374706436774</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43734185843956</v>
+        <v>15.44403243546419</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12411773655752</v>
+        <v>86.1614441136423</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249966707039907</v>
+        <v>3.251375249571408</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.112541133089889</v>
+        <v>4.659374604355362</v>
       </c>
       <c r="C2" t="n">
-        <v>8.59029241215959</v>
+        <v>6.465790380169493</v>
       </c>
       <c r="D2" t="n">
-        <v>36.14009648873358</v>
+        <v>21.28232673266236</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96812640957437</v>
+        <v>19.7920337176157</v>
       </c>
       <c r="C3" t="n">
-        <v>22.83545160078081</v>
+        <v>11.72206758870692</v>
       </c>
       <c r="D3" t="n">
-        <v>51.36994862471436</v>
+        <v>28.63758053287946</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.01943933210246</v>
+        <v>34.35724265782137</v>
       </c>
       <c r="C4" t="n">
-        <v>52.39096623713103</v>
+        <v>19.23341927389927</v>
       </c>
       <c r="D4" t="n">
-        <v>31.57496966398591</v>
+        <v>24.70862622048373</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.70104997629023</v>
+        <v>17.52419652080557</v>
       </c>
       <c r="C5" t="n">
-        <v>44.74315162104839</v>
+        <v>14.70167187109599</v>
       </c>
       <c r="D5" t="n">
-        <v>30.77779052813751</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.6242369756475</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72360921872659</v>
+        <v>16.74264841648745</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0140162342322</v>
+        <v>102.1301553405734</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180902304681647</v>
+        <v>5.022794524946235</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.795256698168921</v>
+        <v>6.273367830137119</v>
       </c>
       <c r="C2" t="n">
-        <v>7.256097282088176</v>
+        <v>3.786600895279947</v>
       </c>
       <c r="D2" t="n">
-        <v>32.15616430490002</v>
+        <v>18.64044366053419</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.91274762750905</v>
+        <v>17.69600236904876</v>
       </c>
       <c r="C3" t="n">
-        <v>28.76029899591031</v>
+        <v>19.5760492226814</v>
       </c>
       <c r="D3" t="n">
-        <v>67.41170611210724</v>
+        <v>38.44033135978386</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.72062817711294</v>
+        <v>36.41204060280995</v>
       </c>
       <c r="C4" t="n">
-        <v>54.98179842863836</v>
+        <v>24.9766433437431</v>
       </c>
       <c r="D4" t="n">
-        <v>49.21304891848411</v>
+        <v>32.78742807873073</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.9483525867692</v>
+        <v>34.95021827118646</v>
       </c>
       <c r="C5" t="n">
-        <v>71.86393195086653</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D5" t="n">
-        <v>34.9993056563988</v>
+        <v>32.00497515844602</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.18366893615217</v>
+        <v>14.77235770580176</v>
       </c>
       <c r="C6" t="n">
-        <v>42.62650357069227</v>
+        <v>18.23400011097601</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="19">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03764300233637</v>
+        <v>18.07753211106051</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6741472057182</v>
+        <v>117.934376153109</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012547667445455</v>
+        <v>6.886678899451621</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.105488972710914</v>
+        <v>6.801548095021903</v>
       </c>
       <c r="C2" t="n">
-        <v>6.021058670145687</v>
+        <v>5.063854658505048</v>
       </c>
       <c r="D2" t="n">
-        <v>31.87342096607695</v>
+        <v>35.24768782557323</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.62942345160922</v>
+        <v>17.77945092390974</v>
       </c>
       <c r="C3" t="n">
-        <v>26.66426764734337</v>
+        <v>15.74723317611884</v>
       </c>
       <c r="D3" t="n">
-        <v>72.31062715629882</v>
+        <v>41.44938807330033</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.39482680802324</v>
+        <v>25.56372847088269</v>
       </c>
       <c r="C4" t="n">
-        <v>53.74381457358314</v>
+        <v>32.22586839190155</v>
       </c>
       <c r="D4" t="n">
-        <v>61.73327739074368</v>
+        <v>38.16053326407352</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.78221624057323</v>
+        <v>27.93072218582176</v>
       </c>
       <c r="C5" t="n">
-        <v>64.45173678380311</v>
+        <v>27.70982895236623</v>
       </c>
       <c r="D5" t="n">
-        <v>35.80924751240241</v>
+        <v>29.74695543867836</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>17.10695374650067</v>
       </c>
       <c r="C6" t="n">
-        <v>53.73596059194917</v>
+        <v>20.7296027751714</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>26.4698816019025</v>
+        <v>15.33097214951819</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5986,7 +5986,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044587463912031</v>
+        <v>7.070555373851541</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04300747417528</v>
+        <v>67.17027605158964</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402867164945019</v>
+        <v>5.302916530388656</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.625013434706723</v>
+        <v>7.056802498126073</v>
       </c>
       <c r="C2" t="n">
-        <v>4.610287219143022</v>
+        <v>5.834526606338795</v>
       </c>
       <c r="D2" t="n">
-        <v>33.65136605846792</v>
+        <v>26.83312825247382</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.22262004915255</v>
+        <v>21.65735435568464</v>
       </c>
       <c r="C3" t="n">
-        <v>24.65659359215864</v>
+        <v>18.45685683984004</v>
       </c>
       <c r="D3" t="n">
-        <v>81.61268665403736</v>
+        <v>62.05136364691965</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.34225440035042</v>
+        <v>31.71535958569321</v>
       </c>
       <c r="C4" t="n">
-        <v>61.89919275276139</v>
+        <v>36.98636300979434</v>
       </c>
       <c r="D4" t="n">
-        <v>85.30602151741385</v>
+        <v>51.68901662859457</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.21266370338984</v>
+        <v>34.41025703385071</v>
       </c>
       <c r="C5" t="n">
-        <v>85.51022503989719</v>
+        <v>47.83565688942584</v>
       </c>
       <c r="D5" t="n">
-        <v>50.29002615004288</v>
+        <v>37.33095645398497</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.80381469006666</v>
+        <v>29.62521872335175</v>
       </c>
       <c r="C6" t="n">
-        <v>81.99262301558088</v>
+        <v>34.93843729873549</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>33.65038431076368</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>55.75443387188061</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>27.95526587842792</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>35.00617789032851</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.260494000491232</v>
+        <v>7.299834507206535</v>
       </c>
       <c r="C21" t="n">
-        <v>75.32762525509654</v>
+        <v>77.56074163906943</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445370500368424</v>
+        <v>6.387355193805718</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.547455366071226</v>
+        <v>6.627778751370216</v>
       </c>
       <c r="C2" t="n">
-        <v>4.005530633326987</v>
+        <v>7.999280294203011</v>
       </c>
       <c r="D2" t="n">
-        <v>29.36701907713484</v>
+        <v>29.81273253486289</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.39166058073225</v>
+        <v>23.43431770037137</v>
       </c>
       <c r="C3" t="n">
-        <v>20.6854241284803</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D3" t="n">
-        <v>89.03469929814324</v>
+        <v>69.5960947540564</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>38.23710958500477</v>
       </c>
       <c r="C4" t="n">
-        <v>61.80985371167493</v>
+        <v>42.65301075870693</v>
       </c>
       <c r="D4" t="n">
-        <v>105.0371868773663</v>
+        <v>72.21147063816989</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.15852871093603</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="C5" t="n">
-        <v>100.6045959926919</v>
+        <v>60.0093284220863</v>
       </c>
       <c r="D5" t="n">
-        <v>69.50773746067419</v>
+        <v>48.10563750809372</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>39.80888765950392</v>
       </c>
       <c r="C6" t="n">
-        <v>111.2555768360656</v>
+        <v>57.9623844587317</v>
       </c>
       <c r="D6" t="n">
-        <v>42.86801350593698</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>26.17044855210722</v>
       </c>
       <c r="C7" t="n">
-        <v>89.47059527882881</v>
+        <v>39.40538935305847</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>51.98844967838984</v>
+        <v>27.28767743954009</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.462706731903255</v>
+        <v>7.518827301911703</v>
       </c>
       <c r="C21" t="n">
-        <v>83.95545073391162</v>
+        <v>87.40636738472354</v>
       </c>
       <c r="D21" t="n">
-        <v>6.529868390415349</v>
+        <v>7.518827301911703</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_3_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_3_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641201189</v>
+        <v>10.84497623971245</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907221995971</v>
+        <v>37.78907161958627</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.055239913345078</v>
+        <v>1.575705065316131</v>
       </c>
       <c r="C2" t="n">
-        <v>12.22766765639402</v>
+        <v>2.468113728476481</v>
       </c>
       <c r="D2" t="n">
-        <v>24.65855708756714</v>
+        <v>20.78065365579224</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.04161861867264</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="C3" t="n">
-        <v>26.96370069713865</v>
+        <v>30.92014394525329</v>
       </c>
       <c r="D3" t="n">
-        <v>76.77267047210057</v>
+        <v>73.1156602737812</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.98934931063608</v>
+        <v>18.78672406846696</v>
       </c>
       <c r="C4" t="n">
-        <v>48.49833658979244</v>
+        <v>98.60477591914113</v>
       </c>
       <c r="D4" t="n">
-        <v>89.14760028413161</v>
+        <v>69.21223140169589</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.53546307610458</v>
+        <v>18.23596360638451</v>
       </c>
       <c r="C5" t="n">
-        <v>70.36676670189014</v>
+        <v>118.0306177430728</v>
       </c>
       <c r="D5" t="n">
-        <v>63.17546476828226</v>
+        <v>45.40583132141499</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.94601354292898</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="C6" t="n">
-        <v>77.32343093418305</v>
+        <v>75.91462297858888</v>
       </c>
       <c r="D6" t="n">
-        <v>44.03531152628644</v>
+        <v>29.34345713223292</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.78845088416398</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>63.24026011676253</v>
+        <v>42.27994663109313</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>29.52409870981433</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.36144738607885</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>40.80634332701867</v>
+        <v>28.95664853675967</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.207811718130833</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>18.41660518396592</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.724790897824544</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.55988622280681</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.690389760052613</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.59403947652733</v>
+        <v>1.387209506100743</v>
       </c>
       <c r="C2" t="n">
-        <v>13.65611056607313</v>
+        <v>5.321072557017713</v>
       </c>
       <c r="D2" t="n">
-        <v>30.63347361561323</v>
+        <v>19.74196458469911</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.16710239836699</v>
+        <v>8.713010875190442</v>
       </c>
       <c r="C3" t="n">
-        <v>38.34706532788041</v>
+        <v>18.48630927096744</v>
       </c>
       <c r="D3" t="n">
-        <v>78.18638716621598</v>
+        <v>72.64442137574274</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.20180772538089</v>
+        <v>21.72214970416493</v>
       </c>
       <c r="C4" t="n">
-        <v>57.80235958293945</v>
+        <v>87.52673482442013</v>
       </c>
       <c r="D4" t="n">
-        <v>105.5221702432642</v>
+        <v>89.14760028413161</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.42594930158544</v>
+        <v>23.34105166846792</v>
       </c>
       <c r="C5" t="n">
-        <v>80.11061266653974</v>
+        <v>152.6863117029852</v>
       </c>
       <c r="D5" t="n">
-        <v>78.29437941368315</v>
+        <v>59.17484287347651</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.52590764096936</v>
+        <v>18.35475507859837</v>
       </c>
       <c r="C6" t="n">
-        <v>93.66560321907546</v>
+        <v>134.5612855871806</v>
       </c>
       <c r="D6" t="n">
-        <v>53.13218575383738</v>
+        <v>36.30699359845555</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.50815406683489</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>87.55422376013904</v>
+        <v>76.59497413763189</v>
       </c>
       <c r="D7" t="n">
-        <v>42.75903951076558</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.29182541453534</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>61.66848204226339</v>
+        <v>42.72566008882119</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.75468624712531</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>40.71405904281946</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.9165501808131</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.8838586683752</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.895687726016375</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.1428364432013</v>
+        <v>0.735329030480861</v>
       </c>
       <c r="C2" t="n">
-        <v>9.389435043416494</v>
+        <v>2.189297380470387</v>
       </c>
       <c r="D2" t="n">
-        <v>40.0435253608189</v>
+        <v>13.29286391550181</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.81567777797563</v>
+        <v>7.898160280665589</v>
       </c>
       <c r="C3" t="n">
-        <v>45.36165267472387</v>
+        <v>20.89649988489336</v>
       </c>
       <c r="D3" t="n">
-        <v>82.65333922053897</v>
+        <v>74.00414194612456</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.74609686416112</v>
+        <v>23.85352397008475</v>
       </c>
       <c r="C4" t="n">
-        <v>75.89989676302515</v>
+        <v>79.4096448057075</v>
       </c>
       <c r="D4" t="n">
-        <v>116.3066687744154</v>
+        <v>103.0589652533089</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.45111488899736</v>
+        <v>23.58648859452962</v>
       </c>
       <c r="C5" t="n">
-        <v>91.37616757277189</v>
+        <v>175.6837516749667</v>
       </c>
       <c r="D5" t="n">
-        <v>95.05772146369743</v>
+        <v>66.97973712223865</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.21397391292614</v>
+        <v>14.69185439405352</v>
       </c>
       <c r="C6" t="n">
-        <v>108.1561993337584</v>
+        <v>171.9148222383632</v>
       </c>
       <c r="D6" t="n">
-        <v>62.71207985187777</v>
+        <v>37.11202671593793</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>58.09001166028376</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>109.8320426649077</v>
+        <v>74.01984990939251</v>
       </c>
       <c r="D7" t="n">
-        <v>47.60985491744906</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>40.3056519978528</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>85.86856295194725</v>
+        <v>40.97324043674063</v>
       </c>
       <c r="D8" t="n">
-        <v>40.88979188187965</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.85468564423824</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>57.243745139223</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>36.86953503298896</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.863979037466197</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>35.7169632282032</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.44199175555609</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.09199337320149</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.299406396471</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.12649088815205</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.14734427109503</v>
+        <v>0.5959208564778139</v>
       </c>
       <c r="C2" t="n">
-        <v>6.234097921967246</v>
+        <v>3.754203221039802</v>
       </c>
       <c r="D2" t="n">
-        <v>32.3485868549324</v>
+        <v>10.20232214253285</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>33.96847056693964</v>
+        <v>5.119814277647116</v>
       </c>
       <c r="C3" t="n">
-        <v>61.13833828197012</v>
+        <v>13.93099992326224</v>
       </c>
       <c r="D3" t="n">
-        <v>91.08655200001907</v>
+        <v>68.35418390818417</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.03518835309942</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C4" t="n">
-        <v>89.32627836630454</v>
+        <v>65.26855087373644</v>
       </c>
       <c r="D4" t="n">
-        <v>110.7293600665893</v>
+        <v>115.36222748293</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.28186906877263</v>
+        <v>29.57514959043517</v>
       </c>
       <c r="C5" t="n">
-        <v>64.62354263204631</v>
+        <v>162.2338081267854</v>
       </c>
       <c r="D5" t="n">
-        <v>63.93631923907354</v>
+        <v>86.34471058850698</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>22.21891404251382</v>
       </c>
       <c r="C6" t="n">
-        <v>72.33222560579226</v>
+        <v>228.186637150382</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>48.1409804254466</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.70942804173872</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>60.36570283872788</v>
+        <v>155.585412673626</v>
       </c>
       <c r="D7" t="n">
-        <v>28.7455727803466</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.18763698469816</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>42.14152020479433</v>
+        <v>66.67539533392211</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>37.38593432542277</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>27.90126975469435</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.115306449753382</v>
+        <v>0.3995713156284518</v>
       </c>
       <c r="C2" t="n">
-        <v>2.728276870101886</v>
+        <v>1.917353266394021</v>
       </c>
       <c r="D2" t="n">
-        <v>21.84094117637879</v>
+        <v>7.162831250184728</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35.56871932486194</v>
+        <v>3.784637399871454</v>
       </c>
       <c r="C3" t="n">
-        <v>42.55876297909924</v>
+        <v>14.47586989911922</v>
       </c>
       <c r="D3" t="n">
-        <v>96.7414187764807</v>
+        <v>62.05627238544088</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.38423287192155</v>
+        <v>16.33628179866692</v>
       </c>
       <c r="C4" t="n">
-        <v>124.3216570318863</v>
+        <v>52.12294911387166</v>
       </c>
       <c r="D4" t="n">
-        <v>128.8524226869854</v>
+        <v>122.5348762101572</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.62610266006477</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C5" t="n">
-        <v>111.6247139728624</v>
+        <v>149.5692627420016</v>
       </c>
       <c r="D5" t="n">
-        <v>81.80412745636549</v>
+        <v>103.5743827980385</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.43153668817465</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>87.94986808495052</v>
+        <v>253.5854320069512</v>
       </c>
       <c r="D6" t="n">
-        <v>38.9233512302733</v>
+        <v>58.80766923208819</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>79.05032514595315</v>
+        <v>220.2629514294059</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>55.40984042768998</v>
+        <v>104.0603479116407</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>48.59062087399162</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.813329067472864</v>
+        <v>1.229148125717006</v>
       </c>
       <c r="C2" t="n">
-        <v>3.849432748351743</v>
+        <v>9.234318906145498</v>
       </c>
       <c r="D2" t="n">
-        <v>19.04786895779661</v>
+        <v>10.6499990956694</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.03380569476767</v>
+        <v>2.572178985126643</v>
       </c>
       <c r="C3" t="n">
-        <v>24.98547907308132</v>
+        <v>10.72068493037517</v>
       </c>
       <c r="D3" t="n">
-        <v>91.87685890193775</v>
+        <v>54.31519173745478</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.07488453409257</v>
+        <v>11.92038062496477</v>
       </c>
       <c r="C4" t="n">
-        <v>115.9620753302247</v>
+        <v>44.43979158043612</v>
       </c>
       <c r="D4" t="n">
-        <v>146.1331457771377</v>
+        <v>125.1384711218197</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.97158004096841</v>
+        <v>28.86338250485623</v>
       </c>
       <c r="C5" t="n">
-        <v>170.4804888424586</v>
+        <v>123.7247544277043</v>
       </c>
       <c r="D5" t="n">
-        <v>106.3969074477481</v>
+        <v>120.7058802371454</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.79129831628549</v>
+        <v>34.17365583712723</v>
       </c>
       <c r="C6" t="n">
-        <v>131.7436696759922</v>
+        <v>247.4671803140851</v>
       </c>
       <c r="D6" t="n">
-        <v>53.01143078621504</v>
+        <v>74.02279515250527</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.77037851486003</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>102.585762859862</v>
+        <v>290.0308520317054</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>45.45393695892307</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.44213062427633</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>78.44164156932014</v>
+        <v>186.5075201142878</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>51.03124566674919</v>
+        <v>82.42655550085793</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>42.93280885441725</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>37.43894870145212</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.012402867256714</v>
+        <v>0.8256498192715676</v>
       </c>
       <c r="C2" t="n">
-        <v>1.811324514335365</v>
+        <v>4.80172802147115</v>
       </c>
       <c r="D2" t="n">
-        <v>13.14462001216054</v>
+        <v>7.667449570167589</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.47559216167874</v>
+        <v>4.226423866782518</v>
       </c>
       <c r="C3" t="n">
-        <v>22.20713307006285</v>
+        <v>21.46591355335651</v>
       </c>
       <c r="D3" t="n">
-        <v>90.04589943351745</v>
+        <v>58.70851271395927</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62.86915948455724</v>
+        <v>19.65458903902115</v>
       </c>
       <c r="C4" t="n">
-        <v>107.5386800277871</v>
+        <v>63.87741437681872</v>
       </c>
       <c r="D4" t="n">
-        <v>157.6068311966702</v>
+        <v>127.9845577164312</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.81235698643118</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>204.5716778724292</v>
+        <v>197.6012691722768</v>
       </c>
       <c r="D5" t="n">
-        <v>116.4107340310656</v>
+        <v>110.4466167277662</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.51203999992289</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>163.6632327841688</v>
+        <v>251.6533525249934</v>
       </c>
       <c r="D6" t="n">
-        <v>51.72337779824321</v>
+        <v>63.15484806649307</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>106.8377121669549</v>
+        <v>131.1516758103314</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>62.16917337142927</v>
+        <v>60.75054793879262</v>
       </c>
       <c r="D8" t="n">
-        <v>32.62838495064274</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.548838024402973</v>
+        <v>0.3926990816987241</v>
       </c>
       <c r="C2" t="n">
-        <v>2.811725424962865</v>
+        <v>3.503857556456866</v>
       </c>
       <c r="D2" t="n">
-        <v>17.0971362694582</v>
+        <v>5.702972413969722</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.29410770511332</v>
+        <v>3.544109212330985</v>
       </c>
       <c r="C3" t="n">
-        <v>14.35315143608837</v>
+        <v>19.99820073550753</v>
       </c>
       <c r="D3" t="n">
-        <v>80.68493507352412</v>
+        <v>51.56629816556372</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>59.5125640837374</v>
+        <v>13.09455087924396</v>
       </c>
       <c r="C4" t="n">
-        <v>82.42164676233671</v>
+        <v>56.14320596276234</v>
       </c>
       <c r="D4" t="n">
-        <v>165.2899887301057</v>
+        <v>123.0836731768311</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>72.1339125695344</v>
+        <v>20.17491532227196</v>
       </c>
       <c r="C5" t="n">
-        <v>201.3073667558085</v>
+        <v>143.8014949795516</v>
       </c>
       <c r="D5" t="n">
-        <v>142.6479414270616</v>
+        <v>116.18984079761</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.99005332089985</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="C6" t="n">
-        <v>239.5376041068835</v>
+        <v>235.2306769283528</v>
       </c>
       <c r="D6" t="n">
-        <v>69.75611962984863</v>
+        <v>68.58882160949918</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>162.7119192587536</v>
+        <v>169.658766014004</v>
       </c>
       <c r="D7" t="n">
-        <v>40.48334833232147</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>96.21618375470864</v>
+        <v>70.09678608322226</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>46.48280855297372</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.995713156284519</v>
+        <v>0.5831581363226054</v>
       </c>
       <c r="C2" t="n">
-        <v>2.14217349066654</v>
+        <v>4.287292224445821</v>
       </c>
       <c r="D2" t="n">
-        <v>13.52848336452105</v>
+        <v>9.892089867990862</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.50380080319464</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C3" t="n">
-        <v>12.91489104936679</v>
+        <v>16.13993225781756</v>
       </c>
       <c r="D3" t="n">
-        <v>76.87084524252526</v>
+        <v>44.16392047554277</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>53.65447553249668</v>
+        <v>9.789006359044947</v>
       </c>
       <c r="C4" t="n">
-        <v>64.4517367838031</v>
+        <v>53.15672944644354</v>
       </c>
       <c r="D4" t="n">
-        <v>167.8297700409922</v>
+        <v>121.4500449969644</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>80.40513697781378</v>
+        <v>20.49398332615217</v>
       </c>
       <c r="C5" t="n">
-        <v>189.2318699935727</v>
+        <v>121.5403657857552</v>
       </c>
       <c r="D5" t="n">
-        <v>161.2275167299325</v>
+        <v>134.6221539448439</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.65674212754145</v>
+        <v>19.8843180018149</v>
       </c>
       <c r="C6" t="n">
-        <v>277.4546639403039</v>
+        <v>235.1904252724787</v>
       </c>
       <c r="D6" t="n">
-        <v>84.44797402390215</v>
+        <v>88.71464954655879</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.71509754378595</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>221.2211371887508</v>
+        <v>259.6683407824643</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05280305851362</v>
+        <v>45.21439051908685</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>126.424560614383</v>
+        <v>150.5411929692059</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>54.80312034646543</v>
+        <v>59.57343244140068</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.102543729598173</v>
+        <v>0.3475386873033709</v>
       </c>
       <c r="C2" t="n">
-        <v>6.185010536754906</v>
+        <v>6.032839642596649</v>
       </c>
       <c r="D2" t="n">
-        <v>17.33373746618168</v>
+        <v>13.46859675456199</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.09222753093697</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C3" t="n">
-        <v>10.67159754516283</v>
+        <v>16.38536918387927</v>
       </c>
       <c r="D3" t="n">
-        <v>70.84291433844984</v>
+        <v>41.88626580169017</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.52011496573511</v>
+        <v>7.070546965985528</v>
       </c>
       <c r="C4" t="n">
-        <v>49.76184588515808</v>
+        <v>46.23933512232053</v>
       </c>
       <c r="D4" t="n">
-        <v>167.3320239549391</v>
+        <v>115.4388038038612</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>80.40513697781378</v>
+        <v>18.06415775814131</v>
       </c>
       <c r="C5" t="n">
-        <v>158.3313610024044</v>
+        <v>109.3666942530947</v>
       </c>
       <c r="D5" t="n">
-        <v>176.4691498383642</v>
+        <v>147.605767333508</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>82.71715282131501</v>
+        <v>23.90948358922682</v>
       </c>
       <c r="C6" t="n">
-        <v>288.0005977793231</v>
+        <v>215.5073655500344</v>
       </c>
       <c r="D6" t="n">
-        <v>107.5121728397725</v>
+        <v>109.041735762989</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.75903951076558</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>296.4986059072834</v>
+        <v>302.0081740235165</v>
       </c>
       <c r="D7" t="n">
-        <v>55.69454726192155</v>
+        <v>57.9103518304066</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>190.5130507476148</v>
+        <v>244.2539200780851</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.106249736236907</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>92.96561710594743</v>
+        <v>121.476552184979</v>
       </c>
       <c r="D9" t="n">
-        <v>34.72343455150543</v>
+        <v>25.73749781453438</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.305585577928015</v>
+        <v>5.011822030179967</v>
       </c>
       <c r="C2" t="n">
-        <v>2.836269117569035</v>
+        <v>8.651160769822893</v>
       </c>
       <c r="D2" t="n">
-        <v>7.536877125502762</v>
+        <v>12.27577329390212</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.367795536194059</v>
+        <v>1.188896469842887</v>
       </c>
       <c r="C2" t="n">
-        <v>3.513675033499335</v>
+        <v>9.991246386119789</v>
       </c>
       <c r="D2" t="n">
-        <v>12.7578114166873</v>
+        <v>12.85696793481623</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.88453898599315</v>
+        <v>1.644427404613407</v>
       </c>
       <c r="C3" t="n">
-        <v>16.29210315197582</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="D3" t="n">
-        <v>77.87713663937824</v>
+        <v>42.52931054797182</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>62.43522699928015</v>
+        <v>5.615596868291756</v>
       </c>
       <c r="C4" t="n">
-        <v>75.98923580411162</v>
+        <v>43.11246868429443</v>
       </c>
       <c r="D4" t="n">
-        <v>170.5354667138965</v>
+        <v>110.8569872681413</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.81740459367266</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="C5" t="n">
-        <v>241.019061392592</v>
+        <v>97.65935287995148</v>
       </c>
       <c r="D5" t="n">
-        <v>160.8593613408399</v>
+        <v>153.1280981698963</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.52584122104457</v>
+        <v>24.51325842733861</v>
       </c>
       <c r="C6" t="n">
-        <v>251.7338558367417</v>
+        <v>197.474623718429</v>
       </c>
       <c r="D6" t="n">
-        <v>84.56872899152451</v>
+        <v>128.0002656796991</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>133.966346478407</v>
+        <v>306.9188760401591</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>72.64245788033423</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.086213871524472</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>68.51126354086365</v>
+        <v>318.5231339043564</v>
       </c>
       <c r="D8" t="n">
-        <v>25.53525778745954</v>
+        <v>40.55599766243574</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>203.0156077611979</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
+        <v>88.68617886313562</v>
+      </c>
+      <c r="D10" t="n">
         <v>22.63419332141022</v>
-      </c>
-      <c r="D10" t="n">
-        <v>19.50241814486289</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>10.14636252339079</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.840237166115028</v>
+        <v>4.87241385617692</v>
       </c>
       <c r="C2" t="n">
-        <v>2.935425635697963</v>
+        <v>9.977501918260334</v>
       </c>
       <c r="D2" t="n">
-        <v>13.23984953947248</v>
+        <v>14.72621556370216</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63218876827272</v>
+        <v>8.276133146800612</v>
       </c>
       <c r="C3" t="n">
-        <v>7.14712328691678</v>
+        <v>17.07750131537327</v>
       </c>
       <c r="D3" t="n">
-        <v>9.468956607460486</v>
+        <v>11.388273369263</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39879599135628</v>
+        <v>11.67776403613186</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14663783710051</v>
+        <v>59.9458553854769</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576328940159562</v>
+        <v>0.7785176024087909</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.824308218668826</v>
+        <v>2.911863690796039</v>
       </c>
       <c r="C2" t="n">
-        <v>3.319288988058466</v>
+        <v>4.867505117655686</v>
       </c>
       <c r="D2" t="n">
-        <v>18.23301836327176</v>
+        <v>14.7586132379423</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.35086914551039</v>
+        <v>13.76410281354028</v>
       </c>
       <c r="C3" t="n">
-        <v>9.88619938176538</v>
+        <v>31.67608967752334</v>
       </c>
       <c r="D3" t="n">
-        <v>18.29977720716055</v>
+        <v>21.48554850744145</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.3437759274024</v>
+        <v>10.27398972494287</v>
       </c>
       <c r="C4" t="n">
-        <v>11.61407534123977</v>
+        <v>28.30771330425253</v>
       </c>
       <c r="D4" t="n">
-        <v>20.0374706436774</v>
+        <v>20.24167416616074</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.58292145661112</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44403243546419</v>
+        <v>13.62858687021711</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1614441136423</v>
+        <v>73.75470541529258</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251375249571408</v>
+        <v>1.603363161202012</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.659374604355362</v>
+        <v>2.402336632291945</v>
       </c>
       <c r="C2" t="n">
-        <v>6.465790380169493</v>
+        <v>6.737734494245859</v>
       </c>
       <c r="D2" t="n">
-        <v>21.28232673266236</v>
+        <v>18.27228827144164</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.7920337176157</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C3" t="n">
-        <v>11.72206758870692</v>
+        <v>23.62575850269949</v>
       </c>
       <c r="D3" t="n">
-        <v>28.63758053287946</v>
+        <v>28.69157665661304</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.35724265782137</v>
+        <v>20.22891144600553</v>
       </c>
       <c r="C4" t="n">
-        <v>19.23341927389927</v>
+        <v>59.88268296823845</v>
       </c>
       <c r="D4" t="n">
-        <v>24.70862622048373</v>
+        <v>26.80171232593792</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.52419652080557</v>
+        <v>9.572040116406402</v>
       </c>
       <c r="C5" t="n">
-        <v>14.70167187109599</v>
+        <v>33.37942194439156</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>27.21895510024282</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>4.427682146153116</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.6242369756475</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74264841648745</v>
+        <v>14.8393726934022</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1301553405734</v>
+        <v>87.38741697225738</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022794524946235</v>
+        <v>2.473228782233699</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.273367830137119</v>
+        <v>2.873575530330414</v>
       </c>
       <c r="C2" t="n">
-        <v>3.786600895279947</v>
+        <v>6.436337949042089</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64044366053419</v>
+        <v>19.63495408493621</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69600236904876</v>
+        <v>9.778207134298231</v>
       </c>
       <c r="C3" t="n">
-        <v>19.5760492226814</v>
+        <v>25.46653544816226</v>
       </c>
       <c r="D3" t="n">
-        <v>38.44033135978386</v>
+        <v>36.64864179953343</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.41204060280995</v>
+        <v>21.90082778633785</v>
       </c>
       <c r="C4" t="n">
-        <v>24.9766433437431</v>
+        <v>58.9254789565978</v>
       </c>
       <c r="D4" t="n">
-        <v>32.78742807873073</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.95021827118646</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="C5" t="n">
-        <v>26.01631416254048</v>
+        <v>78.19620464325845</v>
       </c>
       <c r="D5" t="n">
-        <v>32.00497515844602</v>
+        <v>30.55689729468198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.77235770580176</v>
+        <v>8.895615948180351</v>
       </c>
       <c r="C6" t="n">
-        <v>18.23400011097601</v>
+        <v>34.13340418125311</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>33.81139093426016</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.63820242768521</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07753211106051</v>
+        <v>16.08227997028907</v>
       </c>
       <c r="C21" t="n">
-        <v>117.934376153109</v>
+        <v>101.5722945491941</v>
       </c>
       <c r="D21" t="n">
-        <v>6.886678899451621</v>
+        <v>3.385743151639804</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.801548095021903</v>
+        <v>2.214822820780804</v>
       </c>
       <c r="C2" t="n">
-        <v>5.063854658505048</v>
+        <v>5.890486225480863</v>
       </c>
       <c r="D2" t="n">
-        <v>35.24768782557323</v>
+        <v>28.75931724820606</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.77945092390974</v>
+        <v>9.817477042468104</v>
       </c>
       <c r="C3" t="n">
-        <v>15.74723317611884</v>
+        <v>25.17201113688822</v>
       </c>
       <c r="D3" t="n">
-        <v>41.44938807330033</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.56372847088269</v>
+        <v>20.43311496848886</v>
       </c>
       <c r="C4" t="n">
-        <v>32.22586839190155</v>
+        <v>61.6056501891916</v>
       </c>
       <c r="D4" t="n">
-        <v>38.16053326407352</v>
+        <v>45.05240214788613</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.93072218582176</v>
+        <v>26.8262560185441</v>
       </c>
       <c r="C5" t="n">
-        <v>27.70982895236623</v>
+        <v>94.0023426816321</v>
       </c>
       <c r="D5" t="n">
-        <v>29.74695543867836</v>
+        <v>35.7356164345839</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.10695374650067</v>
+        <v>18.51576170209485</v>
       </c>
       <c r="C6" t="n">
-        <v>20.7296027751714</v>
+        <v>81.63035811271381</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.587527095496098</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>15.33097214951819</v>
+        <v>34.19525428662065</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>36.59071868498287</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.070555373851541</v>
+        <v>17.35109284753726</v>
       </c>
       <c r="C21" t="n">
-        <v>67.17027605158964</v>
+        <v>115.3847674361228</v>
       </c>
       <c r="D21" t="n">
-        <v>5.302916530388656</v>
+        <v>4.337773211884314</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.056802498126073</v>
+        <v>3.82292556033708</v>
       </c>
       <c r="C2" t="n">
-        <v>5.834526606338795</v>
+        <v>9.451285148784043</v>
       </c>
       <c r="D2" t="n">
-        <v>26.83312825247382</v>
+        <v>39.53007131149782</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.65735435568464</v>
+        <v>8.580474935117122</v>
       </c>
       <c r="C3" t="n">
-        <v>18.45685683984004</v>
+        <v>23.84174299763379</v>
       </c>
       <c r="D3" t="n">
-        <v>62.05136364691965</v>
+        <v>54.88460540591794</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.71535958569321</v>
+        <v>19.48867367700343</v>
       </c>
       <c r="C4" t="n">
-        <v>36.98636300979434</v>
+        <v>62.26931163726244</v>
       </c>
       <c r="D4" t="n">
-        <v>51.68901662859457</v>
+        <v>55.40296819376024</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.41025703385071</v>
+        <v>29.01064466049325</v>
       </c>
       <c r="C5" t="n">
-        <v>47.83565688942584</v>
+        <v>104.0161692649496</v>
       </c>
       <c r="D5" t="n">
-        <v>37.33095645398497</v>
+        <v>42.60785036431157</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.62521872335175</v>
+        <v>26.92835777978577</v>
       </c>
       <c r="C6" t="n">
-        <v>34.93843729873549</v>
+        <v>114.113444403128</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>39.28561613314037</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>15.03153909972291</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>75.21758210857362</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>8.678649705541805</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11110172149591</v>
+        <v>35.29873870619407</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.299834507206535</v>
+        <v>17.75105966952716</v>
       </c>
       <c r="C21" t="n">
-        <v>77.56074163906943</v>
+        <v>128.6951826040719</v>
       </c>
       <c r="D21" t="n">
-        <v>6.387355193805718</v>
+        <v>5.325317900858146</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.627778751370216</v>
+        <v>3.335978699030662</v>
       </c>
       <c r="C2" t="n">
-        <v>7.999280294203011</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="D2" t="n">
-        <v>29.81273253486289</v>
+        <v>30.88578277560465</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.43431770037137</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="C3" t="n">
-        <v>21.14193681095506</v>
+        <v>39.6282460819225</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5960947540564</v>
+        <v>62.30661805002381</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.23710958500477</v>
+        <v>13.93689040948772</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65301075870693</v>
+        <v>90.76846574384309</v>
       </c>
       <c r="D4" t="n">
-        <v>72.21147063816989</v>
+        <v>52.42925439759667</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.99425804915732</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="C5" t="n">
-        <v>60.0093284220863</v>
+        <v>68.18237805994099</v>
       </c>
       <c r="D5" t="n">
-        <v>48.10563750809372</v>
+        <v>36.1528592088888</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.80888765950392</v>
+        <v>9.298132506921544</v>
       </c>
       <c r="C6" t="n">
-        <v>57.9623844587317</v>
+        <v>49.50953672516665</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>25.35854320069512</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>39.40538935305847</v>
+        <v>24.79305652304895</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>27.28767743954009</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>25.07187287105504</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.518827301911703</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.40636738472354</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.518827301911703</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
